--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5044</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5047</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5044"/>
+  <dimension ref="A1:D5047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65101,8 +65101,50 @@
         <v>150000</v>
       </c>
     </row>
+    <row r="5045">
+      <c r="A5045" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B5045" s="3" t="n">
+        <v>2604000</v>
+      </c>
+      <c r="C5045" s="3" t="n">
+        <v>2454000</v>
+      </c>
+      <c r="D5045" s="3" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="5046">
+      <c r="A5046" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B5046" s="3" t="n">
+        <v>2602000</v>
+      </c>
+      <c r="C5046" s="3" t="n">
+        <v>2452000</v>
+      </c>
+      <c r="D5046" s="3" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="5047">
+      <c r="A5047" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B5047" s="3" t="n">
+        <v>2592000</v>
+      </c>
+      <c r="C5047" s="3" t="n">
+        <v>2437000</v>
+      </c>
+      <c r="D5047" s="3" t="n">
+        <v>155000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5044"/>
+  <autoFilter ref="A1:D5047"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65152,7 +65194,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-12 14:16:29 WIB</t>
+          <t>2026-09-15 14:56:05 WIB</t>
         </is>
       </c>
     </row>
@@ -65163,7 +65205,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5043</v>
+        <v>5046</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5047</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5049</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5047"/>
+  <dimension ref="A1:D5049"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65143,8 +65143,36 @@
         <v>155000</v>
       </c>
     </row>
+    <row r="5048">
+      <c r="A5048" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B5048" s="3" t="n">
+        <v>2593000</v>
+      </c>
+      <c r="C5048" s="3" t="n">
+        <v>2438000</v>
+      </c>
+      <c r="D5048" s="3" t="n">
+        <v>155000</v>
+      </c>
+    </row>
+    <row r="5049">
+      <c r="A5049" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B5049" s="3" t="n">
+        <v>2598000</v>
+      </c>
+      <c r="C5049" s="3" t="n">
+        <v>2438000</v>
+      </c>
+      <c r="D5049" s="3" t="n">
+        <v>160000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5047"/>
+  <autoFilter ref="A1:D5049"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65194,7 +65222,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 14:56:05 WIB</t>
+          <t>2026-09-17 14:53:30 WIB</t>
         </is>
       </c>
     </row>
@@ -65205,7 +65233,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5046</v>
+        <v>5048</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5049</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5050</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5049"/>
+  <dimension ref="A1:D5050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65171,8 +65171,22 @@
         <v>160000</v>
       </c>
     </row>
+    <row r="5050">
+      <c r="A5050" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B5050" s="3" t="n">
+        <v>2623000</v>
+      </c>
+      <c r="C5050" s="3" t="n">
+        <v>2458000</v>
+      </c>
+      <c r="D5050" s="3" t="n">
+        <v>165000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5049"/>
+  <autoFilter ref="A1:D5050"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65222,7 +65236,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 14:53:30 WIB</t>
+          <t>2026-09-18 14:32:11 WIB</t>
         </is>
       </c>
     </row>
@@ -65233,7 +65247,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5048</v>
+        <v>5049</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5050</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5053</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5050"/>
+  <dimension ref="A1:D5053"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65185,8 +65185,50 @@
         <v>165000</v>
       </c>
     </row>
+    <row r="5051">
+      <c r="A5051" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B5051" s="3" t="n">
+        <v>2638000</v>
+      </c>
+      <c r="C5051" s="3" t="n">
+        <v>2473000</v>
+      </c>
+      <c r="D5051" s="3" t="n">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="5052">
+      <c r="A5052" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B5052" s="3" t="n">
+        <v>2638000</v>
+      </c>
+      <c r="C5052" s="3" t="n">
+        <v>2473000</v>
+      </c>
+      <c r="D5052" s="3" t="n">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="5053">
+      <c r="A5053" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B5053" s="3" t="n">
+        <v>2628000</v>
+      </c>
+      <c r="C5053" s="3" t="n">
+        <v>2463000</v>
+      </c>
+      <c r="D5053" s="3" t="n">
+        <v>165000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5050"/>
+  <autoFilter ref="A1:D5053"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65236,7 +65278,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:32:11 WIB</t>
+          <t>2026-09-21 15:06:22 WIB</t>
         </is>
       </c>
     </row>
@@ -65247,7 +65289,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5049</v>
+        <v>5052</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5053</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5054</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5053"/>
+  <dimension ref="A1:D5054"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65227,8 +65227,22 @@
         <v>165000</v>
       </c>
     </row>
+    <row r="5054">
+      <c r="A5054" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B5054" s="3" t="n">
+        <v>2627000</v>
+      </c>
+      <c r="C5054" s="3" t="n">
+        <v>2462000</v>
+      </c>
+      <c r="D5054" s="3" t="n">
+        <v>165000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5053"/>
+  <autoFilter ref="A1:D5054"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65278,7 +65292,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 15:06:22 WIB</t>
+          <t>2026-09-22 14:51:04 WIB</t>
         </is>
       </c>
     </row>
@@ -65289,7 +65303,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5052</v>
+        <v>5053</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5054</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5055</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5054"/>
+  <dimension ref="A1:D5055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65241,8 +65241,22 @@
         <v>165000</v>
       </c>
     </row>
+    <row r="5055">
+      <c r="A5055" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5055" s="3" t="n">
+        <v>2630000</v>
+      </c>
+      <c r="C5055" s="3" t="n">
+        <v>2465000</v>
+      </c>
+      <c r="D5055" s="3" t="n">
+        <v>165000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5054"/>
+  <autoFilter ref="A1:D5055"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65292,7 +65306,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:51:04 WIB</t>
+          <t>2026-09-23 14:53:15 WIB</t>
         </is>
       </c>
     </row>
@@ -65303,7 +65317,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5053</v>
+        <v>5054</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5055</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5056</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5055"/>
+  <dimension ref="A1:D5056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65255,8 +65255,22 @@
         <v>165000</v>
       </c>
     </row>
+    <row r="5056">
+      <c r="A5056" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B5056" s="3" t="n">
+        <v>2605000</v>
+      </c>
+      <c r="C5056" s="3" t="n">
+        <v>2435000</v>
+      </c>
+      <c r="D5056" s="3" t="n">
+        <v>170000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5055"/>
+  <autoFilter ref="A1:D5056"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65306,7 +65320,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:53:15 WIB</t>
+          <t>2026-09-24 14:43:27 WIB</t>
         </is>
       </c>
     </row>
@@ -65317,7 +65331,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5054</v>
+        <v>5055</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5056</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5057</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5056"/>
+  <dimension ref="A1:D5057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65269,8 +65269,22 @@
         <v>170000</v>
       </c>
     </row>
+    <row r="5057">
+      <c r="A5057" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B5057" s="3" t="n">
+        <v>2590000</v>
+      </c>
+      <c r="C5057" s="3" t="n">
+        <v>2415000</v>
+      </c>
+      <c r="D5057" s="3" t="n">
+        <v>175000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5056"/>
+  <autoFilter ref="A1:D5057"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65320,7 +65334,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:43:27 WIB</t>
+          <t>2026-09-25 15:02:58 WIB</t>
         </is>
       </c>
     </row>
@@ -65331,7 +65345,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5055</v>
+        <v>5056</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5057</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5061</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5057"/>
+  <dimension ref="A1:D5061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65283,8 +65283,64 @@
         <v>175000</v>
       </c>
     </row>
+    <row r="5058">
+      <c r="A5058" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B5058" s="3" t="n">
+        <v>2613000</v>
+      </c>
+      <c r="C5058" s="3" t="n">
+        <v>2438000</v>
+      </c>
+      <c r="D5058" s="3" t="n">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="5059">
+      <c r="A5059" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B5059" s="3" t="n">
+        <v>2613000</v>
+      </c>
+      <c r="C5059" s="3" t="n">
+        <v>2438000</v>
+      </c>
+      <c r="D5059" s="3" t="n">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="5060">
+      <c r="A5060" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B5060" s="3" t="n">
+        <v>2597000</v>
+      </c>
+      <c r="C5060" s="3" t="n">
+        <v>2422000</v>
+      </c>
+      <c r="D5060" s="3" t="n">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="5061">
+      <c r="A5061" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B5061" s="3" t="n">
+        <v>2580000</v>
+      </c>
+      <c r="C5061" s="3" t="n">
+        <v>2375000</v>
+      </c>
+      <c r="D5061" s="3" t="n">
+        <v>205000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5057"/>
+  <autoFilter ref="A1:D5061"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65334,7 +65390,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:02:58 WIB</t>
+          <t>2026-09-29 15:49:22 WIB</t>
         </is>
       </c>
     </row>
@@ -65345,7 +65401,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5056</v>
+        <v>5060</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5061</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5063</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5061"/>
+  <dimension ref="A1:D5063"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65339,8 +65339,36 @@
         <v>205000</v>
       </c>
     </row>
+    <row r="5062">
+      <c r="A5062" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B5062" s="3" t="n">
+        <v>2595000</v>
+      </c>
+      <c r="C5062" s="3" t="n">
+        <v>2405000</v>
+      </c>
+      <c r="D5062" s="3" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="5063">
+      <c r="A5063" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B5063" s="3" t="n">
+        <v>2581000</v>
+      </c>
+      <c r="C5063" s="3" t="n">
+        <v>2391000</v>
+      </c>
+      <c r="D5063" s="3" t="n">
+        <v>190000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5061"/>
+  <autoFilter ref="A1:D5063"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65390,7 +65418,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 15:49:22 WIB</t>
+          <t>2026-10-01 16:13:10 WIB</t>
         </is>
       </c>
     </row>
@@ -65401,7 +65429,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5060</v>
+        <v>5062</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5063</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5067</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5063"/>
+  <dimension ref="A1:D5067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65367,8 +65367,64 @@
         <v>190000</v>
       </c>
     </row>
+    <row r="5064">
+      <c r="A5064" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B5064" s="3" t="n">
+        <v>2576000</v>
+      </c>
+      <c r="C5064" s="3" t="n">
+        <v>2386000</v>
+      </c>
+      <c r="D5064" s="3" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="5065">
+      <c r="A5065" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B5065" s="3" t="n">
+        <v>2574000</v>
+      </c>
+      <c r="C5065" s="3" t="n">
+        <v>2380000</v>
+      </c>
+      <c r="D5065" s="3" t="n">
+        <v>194000</v>
+      </c>
+    </row>
+    <row r="5066">
+      <c r="A5066" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B5066" s="3" t="n">
+        <v>2574000</v>
+      </c>
+      <c r="C5066" s="3" t="n">
+        <v>2380000</v>
+      </c>
+      <c r="D5066" s="3" t="n">
+        <v>194000</v>
+      </c>
+    </row>
+    <row r="5067">
+      <c r="A5067" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B5067" s="3" t="n">
+        <v>2580000</v>
+      </c>
+      <c r="C5067" s="3" t="n">
+        <v>2386000</v>
+      </c>
+      <c r="D5067" s="3" t="n">
+        <v>194000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5063"/>
+  <autoFilter ref="A1:D5067"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65418,7 +65474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-01 16:13:10 WIB</t>
+          <t>2026-10-05 16:22:26 WIB</t>
         </is>
       </c>
     </row>
@@ -65429,7 +65485,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5062</v>
+        <v>5066</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5067</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5072</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5067"/>
+  <dimension ref="A1:D5072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65423,8 +65423,78 @@
         <v>194000</v>
       </c>
     </row>
+    <row r="5068">
+      <c r="A5068" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B5068" s="3" t="n">
+        <v>2570000</v>
+      </c>
+      <c r="C5068" s="3" t="n">
+        <v>2376000</v>
+      </c>
+      <c r="D5068" s="3" t="n">
+        <v>194000</v>
+      </c>
+    </row>
+    <row r="5069">
+      <c r="A5069" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B5069" s="3" t="n">
+        <v>2580000</v>
+      </c>
+      <c r="C5069" s="3" t="n">
+        <v>2391000</v>
+      </c>
+      <c r="D5069" s="3" t="n">
+        <v>189000</v>
+      </c>
+    </row>
+    <row r="5070">
+      <c r="A5070" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B5070" s="3" t="n">
+        <v>2565000</v>
+      </c>
+      <c r="C5070" s="3" t="n">
+        <v>2366000</v>
+      </c>
+      <c r="D5070" s="3" t="n">
+        <v>199000</v>
+      </c>
+    </row>
+    <row r="5071">
+      <c r="A5071" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B5071" s="3" t="n">
+        <v>2572000</v>
+      </c>
+      <c r="C5071" s="3" t="n">
+        <v>2376000</v>
+      </c>
+      <c r="D5071" s="3" t="n">
+        <v>196000</v>
+      </c>
+    </row>
+    <row r="5072">
+      <c r="A5072" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B5072" s="3" t="n">
+        <v>2592000</v>
+      </c>
+      <c r="C5072" s="3" t="n">
+        <v>2401000</v>
+      </c>
+      <c r="D5072" s="3" t="n">
+        <v>191000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5067"/>
+  <autoFilter ref="A1:D5072"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65474,7 +65544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05 16:22:26 WIB</t>
+          <t>2026-10-10 15:45:23 WIB</t>
         </is>
       </c>
     </row>
@@ -65485,7 +65555,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5066</v>
+        <v>5071</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5072</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5074</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5072"/>
+  <dimension ref="A1:D5074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65493,8 +65493,36 @@
         <v>191000</v>
       </c>
     </row>
+    <row r="5073">
+      <c r="A5073" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B5073" s="3" t="n">
+        <v>2592000</v>
+      </c>
+      <c r="C5073" s="3" t="n">
+        <v>2401000</v>
+      </c>
+      <c r="D5073" s="3" t="n">
+        <v>191000</v>
+      </c>
+    </row>
+    <row r="5074">
+      <c r="A5074" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B5074" s="3" t="n">
+        <v>2594000</v>
+      </c>
+      <c r="C5074" s="3" t="n">
+        <v>2408000</v>
+      </c>
+      <c r="D5074" s="3" t="n">
+        <v>186000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5072"/>
+  <autoFilter ref="A1:D5074"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65544,7 +65572,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:45:23 WIB</t>
+          <t>2026-10-12 16:31:59 WIB</t>
         </is>
       </c>
     </row>
@@ -65555,7 +65583,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5071</v>
+        <v>5073</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5074</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5075</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5074"/>
+  <dimension ref="A1:D5075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65521,8 +65521,22 @@
         <v>186000</v>
       </c>
     </row>
+    <row r="5075">
+      <c r="A5075" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B5075" s="3" t="n">
+        <v>2574000</v>
+      </c>
+      <c r="C5075" s="3" t="n">
+        <v>2383000</v>
+      </c>
+      <c r="D5075" s="3" t="n">
+        <v>191000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5074"/>
+  <autoFilter ref="A1:D5075"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65572,7 +65586,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 16:31:59 WIB</t>
+          <t>2026-10-13 16:37:51 WIB</t>
         </is>
       </c>
     </row>
@@ -65583,7 +65597,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5073</v>
+        <v>5074</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5075</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5076</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5075"/>
+  <dimension ref="A1:D5076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65535,8 +65535,22 @@
         <v>191000</v>
       </c>
     </row>
+    <row r="5076">
+      <c r="A5076" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B5076" s="3" t="n">
+        <v>2574000</v>
+      </c>
+      <c r="C5076" s="3" t="n">
+        <v>2383000</v>
+      </c>
+      <c r="D5076" s="3" t="n">
+        <v>191000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5075"/>
+  <autoFilter ref="A1:D5076"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65586,7 +65600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-13 16:37:51 WIB</t>
+          <t>2026-10-14 14:52:25 WIB</t>
         </is>
       </c>
     </row>
@@ -65597,7 +65611,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5074</v>
+        <v>5075</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5076</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5077</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5076"/>
+  <dimension ref="A1:D5077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65549,8 +65549,22 @@
         <v>191000</v>
       </c>
     </row>
+    <row r="5077">
+      <c r="A5077" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B5077" s="3" t="n">
+        <v>2561000</v>
+      </c>
+      <c r="C5077" s="3" t="n">
+        <v>2370000</v>
+      </c>
+      <c r="D5077" s="3" t="n">
+        <v>191000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5076"/>
+  <autoFilter ref="A1:D5077"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65600,7 +65614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 14:52:25 WIB</t>
+          <t>2026-10-15 14:37:40 WIB</t>
         </is>
       </c>
     </row>
@@ -65611,7 +65625,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5075</v>
+        <v>5076</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5077</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5078</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5077"/>
+  <dimension ref="A1:D5078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65563,8 +65563,22 @@
         <v>191000</v>
       </c>
     </row>
+    <row r="5078">
+      <c r="A5078" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B5078" s="3" t="n">
+        <v>2565000</v>
+      </c>
+      <c r="C5078" s="3" t="n">
+        <v>2375000</v>
+      </c>
+      <c r="D5078" s="3" t="n">
+        <v>190000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5077"/>
+  <autoFilter ref="A1:D5078"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65614,7 +65628,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-15 14:37:40 WIB</t>
+          <t>2026-10-16 14:24:33 WIB</t>
         </is>
       </c>
     </row>
@@ -65625,7 +65639,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5076</v>
+        <v>5077</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5078</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5079</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5078"/>
+  <dimension ref="A1:D5079"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65577,8 +65577,22 @@
         <v>190000</v>
       </c>
     </row>
+    <row r="5079">
+      <c r="A5079" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B5079" s="3" t="n">
+        <v>2572000</v>
+      </c>
+      <c r="C5079" s="3" t="n">
+        <v>2387000</v>
+      </c>
+      <c r="D5079" s="3" t="n">
+        <v>185000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5078"/>
+  <autoFilter ref="A1:D5079"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65628,7 +65642,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16 14:24:33 WIB</t>
+          <t>2026-10-17 14:06:06 WIB</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5077</v>
+        <v>5078</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5079</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5081</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5079"/>
+  <dimension ref="A1:D5081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65591,8 +65591,36 @@
         <v>185000</v>
       </c>
     </row>
+    <row r="5080">
+      <c r="A5080" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B5080" s="3" t="n">
+        <v>2572000</v>
+      </c>
+      <c r="C5080" s="3" t="n">
+        <v>2387000</v>
+      </c>
+      <c r="D5080" s="3" t="n">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="5081">
+      <c r="A5081" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B5081" s="3" t="n">
+        <v>2574000</v>
+      </c>
+      <c r="C5081" s="3" t="n">
+        <v>2389000</v>
+      </c>
+      <c r="D5081" s="3" t="n">
+        <v>185000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5079"/>
+  <autoFilter ref="A1:D5081"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65642,7 +65670,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17 14:06:06 WIB</t>
+          <t>2026-10-19 14:59:16 WIB</t>
         </is>
       </c>
     </row>
@@ -65653,7 +65681,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5078</v>
+        <v>5080</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5081</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5082</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5081"/>
+  <dimension ref="A1:D5082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65619,8 +65619,22 @@
         <v>185000</v>
       </c>
     </row>
+    <row r="5082">
+      <c r="A5082" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B5082" s="3" t="n">
+        <v>2564000</v>
+      </c>
+      <c r="C5082" s="3" t="n">
+        <v>2379000</v>
+      </c>
+      <c r="D5082" s="3" t="n">
+        <v>185000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5081"/>
+  <autoFilter ref="A1:D5082"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65670,7 +65684,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-19 14:59:16 WIB</t>
+          <t>2026-10-20 14:49:04 WIB</t>
         </is>
       </c>
     </row>
@@ -65681,7 +65695,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5080</v>
+        <v>5081</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5082</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5083</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5082"/>
+  <dimension ref="A1:D5083"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65633,8 +65633,22 @@
         <v>185000</v>
       </c>
     </row>
+    <row r="5083">
+      <c r="A5083" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B5083" s="3" t="n">
+        <v>2554000</v>
+      </c>
+      <c r="C5083" s="3" t="n">
+        <v>2369000</v>
+      </c>
+      <c r="D5083" s="3" t="n">
+        <v>185000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5082"/>
+  <autoFilter ref="A1:D5083"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65684,7 +65698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:49:04 WIB</t>
+          <t>2026-10-21 14:52:54 WIB</t>
         </is>
       </c>
     </row>
@@ -65695,7 +65709,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5081</v>
+        <v>5082</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5083</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5084</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5083"/>
+  <dimension ref="A1:D5084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65647,8 +65647,22 @@
         <v>185000</v>
       </c>
     </row>
+    <row r="5084">
+      <c r="A5084" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B5084" s="3" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="C5084" s="3" t="n">
+        <v>2365000</v>
+      </c>
+      <c r="D5084" s="3" t="n">
+        <v>185000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5083"/>
+  <autoFilter ref="A1:D5084"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65698,7 +65712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:52:54 WIB</t>
+          <t>2026-10-22 14:48:58 WIB</t>
         </is>
       </c>
     </row>
@@ -65709,7 +65723,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5082</v>
+        <v>5083</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5084</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5085</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5084"/>
+  <dimension ref="A1:D5085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65661,8 +65661,22 @@
         <v>185000</v>
       </c>
     </row>
+    <row r="5085">
+      <c r="A5085" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B5085" s="3" t="n">
+        <v>2540000</v>
+      </c>
+      <c r="C5085" s="3" t="n">
+        <v>2335000</v>
+      </c>
+      <c r="D5085" s="3" t="n">
+        <v>205000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5084"/>
+  <autoFilter ref="A1:D5085"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65712,7 +65726,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:48:58 WIB</t>
+          <t>2026-10-23 14:48:01 WIB</t>
         </is>
       </c>
     </row>
@@ -65723,7 +65737,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5083</v>
+        <v>5084</v>
       </c>
     </row>
   </sheetData>
